--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/region-de-los-lagos.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/region-de-los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2324-1188-CM26</t>
+          <t>2297-53-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>DISTRIBUIDORA Y COMERCIALIZADORA SANTA ELIANA SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>77.544.929-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2610.76</v>
+        <v>31611.01</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2324-1189-CM26</t>
+          <t>2297-102-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>FRANCISCO JAVIER GIACAMAN HASBUN CONFECCION Y BORDADOS EMPRESA INDIVID</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.238.721-2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>10302.03</v>
+        <v>8889.76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2324-1192-CM26</t>
+          <t>2297-153-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>INVERSIONES SANTA FRANCISCA SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>77.721.515-9</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>33859</v>
+        <v>7620.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2297-1126-CM26</t>
+          <t>1063538-8710-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>61.602.260-1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>HOSPITAL BASE OSORNO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,6 +752,1165 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
+        <v>364.95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1126922-334-CM25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>62.000.800-1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SCANNO SPA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>77.055.785-2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>16081.77</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2297-251-CM25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>69.210.100-6</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ALEJANDRO IGLESIAS SOTO</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>8.751.811-6</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>1184.21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1126922-386-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>62.000.800-1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SCANNO SPA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>77.055.785-2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>72853.21000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2297-345-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>69.210.100-6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>76.287.511-k</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>50490.06</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2297-601-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>69.210.100-6</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>1828.12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2852-390-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>69.220.200-7</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>10860.15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2852-391-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>69.220.200-7</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SURTI VENTAS S.A.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>76.462.500-5</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>4772.45</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1057539-18103-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Hales Hnos y Cia Ltda</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>1180.21</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2324-930-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>78.094.280-0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>769.52</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2324-956-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>GIORGIO STEFANO RATTO ANDAUR</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>15.775.663-k</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>21326.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2297-1123-CM25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.210.100-6</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>4580.31</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2297-1124-CM25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>69.210.100-6</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>1156.62</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2324-1146-CM25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>12353.87</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3888-435-CM25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>69.251.800-4</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>76.566.610-4</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>15410.46</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3888-442-CM25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>69.251.800-4</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>FUNDACION VIVIENDA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>70.016.130-7</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>7917.57</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2324-1188-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>2610.76</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2324-1189-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>10302.03</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2324-1192-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>33859</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2297-1126-CM26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>69.210.100-6</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
         <v>3167.87</v>
       </c>
     </row>
